--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/03-test-cases/CYC-4-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/03-test-cases/CYC-4-test-cases.xlsx
@@ -3635,7 +3635,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-05T16:04:45.960Z</t>
+    <t>2026-10-05T16:27:31.765Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/03-test-cases/CYC-4-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/03-test-cases/CYC-4-test-cases.xlsx
@@ -3635,7 +3635,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-05T16:27:31.765Z</t>
+    <t>2026-10-05T16:58:06.528Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/03-test-cases/CYC-4-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/03-test-cases/CYC-4-test-cases.xlsx
@@ -3635,7 +3635,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-05T16:58:06.528Z</t>
+    <t>2026-10-05T17:11:12.762Z</t>
   </si>
   <si>
     <t>Column order</t>
